--- a/PythonDataScience/file2.xlsx
+++ b/PythonDataScience/file2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,16 @@
           <t>Taxpaid</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -534,6 +544,14 @@
       <c r="L2" t="n">
         <v>29.76</v>
       </c>
+      <c r="M2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>ez</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -584,6 +602,14 @@
       <c r="L3" t="n">
         <v>38.78</v>
       </c>
+      <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>nz</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -634,6 +660,14 @@
       <c r="L4" t="n">
         <v>34.74</v>
       </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>sz</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -684,6 +718,14 @@
       <c r="L5" t="n">
         <v>38.28</v>
       </c>
+      <c r="M5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>sz</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -734,6 +776,14 @@
       <c r="L6" t="n">
         <v>15</v>
       </c>
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>nz</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -784,6 +834,14 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>sz</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -834,6 +892,14 @@
       <c r="L8" t="n">
         <v>6.78</v>
       </c>
+      <c r="M8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>ez</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -884,6 +950,14 @@
       <c r="L9" t="n">
         <v>20.25</v>
       </c>
+      <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>nz</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -934,6 +1008,14 @@
       <c r="L10" t="n">
         <v>33.72</v>
       </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>sz</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -984,6 +1066,14 @@
       <c r="L11" t="n">
         <v>19.65</v>
       </c>
+      <c r="M11" t="n">
+        <v>4</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>sz</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1034,6 +1124,10 @@
       <c r="L12" t="n">
         <v>37.8</v>
       </c>
+      <c r="M12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1083,6 +1177,14 @@
       </c>
       <c r="L13" t="n">
         <v>34.27</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>nz</t>
+        </is>
       </c>
     </row>
   </sheetData>
